--- a/dados/info_delegacias/dados_deams_filtrados.xlsx
+++ b/dados/info_delegacias/dados_deams_filtrados.xlsx
@@ -6341,7 +6341,9 @@
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr"/>
+      <c r="E235" t="n">
+        <v>2023</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6360,7 +6362,9 @@
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
-      <c r="E236" t="inlineStr"/>
+      <c r="E236" t="n">
+        <v>2016</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6379,7 +6383,9 @@
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
-      <c r="E237" t="inlineStr"/>
+      <c r="E237" t="n">
+        <v>2014</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6402,10 +6408,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E238" t="n">
+        <v>2018</v>
       </c>
     </row>
     <row r="239">
@@ -6429,10 +6433,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E239" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="240">
@@ -6456,10 +6458,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E240" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="241">
@@ -6618,10 +6618,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E246" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="247">
@@ -6861,10 +6859,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E255" t="n">
+        <v>2021</v>
       </c>
     </row>
     <row r="256">
@@ -7565,7 +7561,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Comercial</t>
         </is>
       </c>
     </row>
@@ -8211,10 +8207,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E305" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="306">
@@ -8238,10 +8232,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E306" t="n">
+        <v>2016</v>
       </c>
     </row>
     <row r="307">
@@ -8346,10 +8338,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E310" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="311">
@@ -8400,10 +8390,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E312" t="n">
+        <v>2019</v>
       </c>
     </row>
     <row r="313">
@@ -8508,10 +8496,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E316" t="n">
+        <v>2016</v>
       </c>
     </row>
     <row r="317">
@@ -8774,7 +8760,11 @@
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
-      <c r="E326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -8793,7 +8783,11 @@
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
-      <c r="E327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -8812,7 +8806,11 @@
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Comercial</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -8831,7 +8829,9 @@
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
-      <c r="E329" t="inlineStr"/>
+      <c r="E329" t="n">
+        <v>2019</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Comercial</t>
         </is>
       </c>
     </row>
@@ -9043,10 +9043,8 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
+      <c r="E337" t="n">
+        <v>2017</v>
       </c>
     </row>
     <row r="338">
@@ -9126,7 +9124,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Comercial</t>
         </is>
       </c>
     </row>
